--- a/data/modelling/clustering/tv/df_centroids_values.xlsx
+++ b/data/modelling/clustering/tv/df_centroids_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,20 +613,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero buenos</t>
+          <t>Los de menor calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59415</v>
+        <v>72695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Noblex</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B4319FK5</t>
+          <t>PLD39HS21LCH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dolby Audio</t>
+          <t>Surround</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>3840 px - 2160 px</t>
+          <t>1366 px - 768 px</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>280 cd/m²</t>
+          <t>200 cd/m²</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -695,22 +695,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>123 cm x 7.9 cm x 71.4 cm</t>
+          <t>73.7 cm x 7.4 cm x 43.8 cm</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>YouTube, Netflix, Web browser</t>
+          <t>Netflix, YouTube</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SV1300</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Saphi</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>9.5 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110269</v>
+        <v>94248</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HYLED-40FHD5A</t>
+          <t>UN55AU7000G</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>50 "</t>
+          <t>55 "</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8 ms</t>
+          <t>6.5 ms</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>737.4 mm x 74.1 mm x 438 mm</t>
+          <t>1230.5 mm x 59.9 mm x 707.2 mm</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>13.9 kg</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -967,20 +967,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Tradicionales</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77403</v>
+        <v>70284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Noblex</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AND50FXUHD</t>
+          <t>DJ50X6500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Surround</t>
+          <t>Dolby Audio</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>32 "</t>
+          <t>43 "</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1366 px - 768 px</t>
+          <t>3840 px - 2160 px</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>220 cd/m²</t>
+          <t>280 cd/m²</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>73.7 cm x 7.4 cm x 43.8 cm</t>
+          <t>112.5 cm x 24.1 cm x 71 cm</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3.9 kg</t>
+          <t>9.5 kg</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1200:1</t>
+          <t>4000:1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1136,6 +1136,183 @@
         </is>
       </c>
       <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Calidad a alto costo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>122895</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HYLED-40FHD5A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Dolby Digital Plus</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>32 "</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3840 px - 2160 px</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>220 cd/m²</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>8 ms</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>737.4 mm x 74.1 mm x 438 mm</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>YouTube, Netflix, Web browser</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>AI ThinQ</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Android TV</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4 kg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>20 W</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>3000:1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/data/modelling/clustering/tv/df_centroids_values.xlsx
+++ b/data/modelling/clustering/tv/df_centroids_values.xlsx
@@ -441,183 +441,183 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Es smart</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sistema operativo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Con apagado automático</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ancho x Profundidad x Altura</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Con función screen share</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Apps integradas</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Con HDR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Resolución máxima</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Cantidad de puertos HDMI</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Cantidad de puertos USB</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Con Wi-Fi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Con Bluetooth</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Con ethernet</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Con entrada S/PDIF</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Con entrada de antena RF</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Cantidad de parlantes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Modos de sonido</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de pantalla</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de resolución</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Resolución máxima</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Frecuencia de actualización de la pantalla</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Con comando de voz integrado</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Asistentes virtuales integrados</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Brillo</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Tiempo de respuesta</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Frecuencia de actualización de la pantalla</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Ancho x Profundidad x Altura</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Apps integradas</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Sistema operativo</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Con apagado automático</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Con función screen share</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Con HDR</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Con Bluetooth</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Con entrada S/PDIF</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Con entrada de antena RF</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Potencia máxima de los parlantes</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Es 3D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Es curvo</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Es portátil</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Relación de contraste</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Es 3D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Es curvo</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Con entrada por video compuesto</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Con VGA</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Con comando de voz integrado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los de menor calidad</t>
+          <t>Alta calidad a buen precio</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72695</v>
+        <v>124735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -626,300 +626,302 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLD39HS21LCH</t>
+          <t>AI ThinQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+          <t>UN50AU7000G</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Android TV</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1116.8 mm x 59.9 mm x 644.2 mm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11.4 kg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>YouTube, Netflix, Web browser</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>50 "</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3840 px - 2160 px</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Surround</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>32 "</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1366 px - 768 px</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>200 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20 W</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Dolby Digital Plus</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Google Assistant</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>250 cd/m²</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>8 ms</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>60 Hz</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>73.7 cm x 7.4 cm x 43.8 cm</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Netflix, YouTube</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Smart</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Saphi</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4 kg</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>16 W</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>3000:1</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>5000:1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Barato pero calidad madia/baja</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94248</v>
+        <v>77992</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UN55AU7000G</t>
+          <t>6800 Series</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+          <t>43PFD6825</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saphi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>955.1 mm x 71.8 mm x 557.9 mm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9.5 kg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YouTube, Netflix, Web browser</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>50 "</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3840 px - 2160 px</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Dolby Audio</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>55 "</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>4K</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>3840 px - 2160 px</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>300 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>6.5 ms</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16 W</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Surround</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>60 Hz</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>1230.5 mm x 59.9 mm x 707.2 mm</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>YouTube, Netflix, Web browser</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>AI ThinQ</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Android TV</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>13.9 kg</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -927,15 +929,17 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20 W</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>4</v>
+          <t>Google Assistant</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>280 cd/m²</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5000:1</t>
+          <t>8 ms</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -950,12 +954,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>4000:1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -967,154 +971,156 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Tradicionales</t>
+          <t>Calidad media/baja a precio medio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70284</v>
+        <v>189543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Noblex</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DJ50X6500</t>
+          <t>Series Q</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+          <t>DK32X5000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>97 cm x 19.5 cm x 61.4 cm</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4 kg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Netflix, YouTube</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>32 "</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1366 px - 768 px</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="S4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Dolby Audio</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>43 "</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4K</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>3840 px - 2160 px</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>280 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16 W</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Google Assistant</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>200 cd/m²</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>8 ms</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>60 Hz</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>112.5 cm x 24.1 cm x 71 cm</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>YouTube, Netflix, Web browser</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>6800 Series</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Saphi</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>9.5 kg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>16 W</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>4000:1</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
           <t>No</t>
@@ -1127,12 +1133,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3000:1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1144,11 +1150,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Calidad a alto costo</t>
+          <t>Alta calidad pero precio alto</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122895</v>
+        <v>440210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1157,141 +1163,143 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HYLED-40FHD5A</t>
+          <t>AI ThinQ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
+          <t>QN55Q60AAG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tizen</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1668.3 mm x 17.2 mm x 955.6 mm</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>32.1 kg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>YouTube, Netflix, Web browser</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>55 "</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3840 px - 2160 px</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20 W</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Dolby Digital Plus</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>32 "</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4K</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>3840 px - 2160 px</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>220 cd/m²</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>60 Hz</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Bixby</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>330 cd/m²</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>8 ms</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>60 Hz</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>737.4 mm x 74.1 mm x 438 mm</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>YouTube, Netflix, Web browser</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>AI ThinQ</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Android TV</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4 kg</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>20 W</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>3000:1</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>No</t>
@@ -1304,12 +1312,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>5000:1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">

--- a/data/modelling/clustering/tv/df_centroids_values.xlsx
+++ b/data/modelling/clustering/tv/df_centroids_values.xlsx
@@ -792,7 +792,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
       <c r="B3" t="n">
